--- a/backend/data/financials_by_company/0533.HK.xlsx
+++ b/backend/data/financials_by_company/0533.HK.xlsx
@@ -632,506 +632,506 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>0.110447</v>
+        <v>0.187</v>
       </c>
       <c r="D2" t="n">
-        <v>158836000</v>
+        <v>294706000</v>
       </c>
       <c r="E2" t="n">
-        <v>93097000</v>
+        <v>221043000</v>
       </c>
       <c r="F2" t="n">
-        <v>52654000</v>
+        <v>32654000</v>
       </c>
       <c r="G2" t="n">
-        <v>524132000</v>
+        <v>503857000</v>
       </c>
       <c r="H2" t="n">
-        <v>158836000</v>
+        <v>294706000</v>
       </c>
       <c r="I2" t="n">
-        <v>106182000</v>
+        <v>262052000</v>
       </c>
       <c r="J2" t="n">
-        <v>24165000</v>
+        <v>20203000</v>
       </c>
       <c r="K2" t="n">
-        <v>1516000</v>
+        <v>1001000</v>
       </c>
       <c r="L2" t="n">
-        <v>25681000</v>
+        <v>21204000</v>
       </c>
       <c r="M2" t="n">
-        <v>93097000</v>
+        <v>221043000</v>
       </c>
       <c r="N2" t="n">
-        <v>93097000</v>
+        <v>221043000</v>
       </c>
       <c r="O2" t="n">
-        <v>1111250000</v>
+        <v>1104559000</v>
       </c>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>80501000</v>
+        <v>240848000</v>
       </c>
       <c r="R2" t="n">
-        <v>973844035</v>
+        <v>982114035</v>
       </c>
       <c r="S2" t="n">
-        <v>973844035</v>
+        <v>982114035</v>
       </c>
       <c r="T2" t="n">
-        <v>0.0956</v>
+        <v>0.2251</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0956</v>
+        <v>0.2251</v>
       </c>
       <c r="V2" t="n">
-        <v>93097000</v>
+        <v>221043000</v>
       </c>
       <c r="W2" t="n">
-        <v>93097000</v>
+        <v>221043000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>93097000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>-9000</v>
-      </c>
+        <v>221043000</v>
+      </c>
+      <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="n">
-        <v>93106000</v>
+        <v>221043000</v>
       </c>
       <c r="AB2" t="n">
-        <v>93106000</v>
+        <v>221043000</v>
       </c>
       <c r="AC2" t="n">
-        <v>11560000</v>
+        <v>40008000</v>
       </c>
       <c r="AD2" t="n">
-        <v>104666000</v>
+        <v>261051000</v>
       </c>
       <c r="AE2" t="n">
-        <v>24165000</v>
+        <v>20203000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1516000</v>
+        <v>1001000</v>
       </c>
       <c r="AG2" t="n">
-        <v>25681000</v>
+        <v>21204000</v>
       </c>
       <c r="AH2" t="n">
-        <v>107863000</v>
+        <v>267625000</v>
       </c>
       <c r="AI2" t="n">
-        <v>587118000</v>
+        <v>600702000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>587118000</v>
+        <v>600702000</v>
       </c>
       <c r="AK2" t="n">
-        <v>431341000</v>
+        <v>430022000</v>
       </c>
       <c r="AL2" t="n">
-        <v>155777000</v>
+        <v>170680000</v>
       </c>
       <c r="AM2" t="n">
-        <v>694981000</v>
+        <v>868327000</v>
       </c>
       <c r="AN2" t="n">
-        <v>524132000</v>
+        <v>503857000</v>
       </c>
       <c r="AO2" t="n">
-        <v>1219113000</v>
+        <v>1372184000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1219113000</v>
+        <v>1372184000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0.088431</v>
+        <v>0.113001</v>
       </c>
       <c r="D3" t="n">
-        <v>174665000</v>
+        <v>216534000</v>
       </c>
       <c r="E3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="F3" t="n">
-        <v>45489000</v>
+        <v>41101000</v>
       </c>
       <c r="G3" t="n">
-        <v>572941000</v>
+        <v>645919000</v>
       </c>
       <c r="H3" t="n">
-        <v>174665000</v>
+        <v>216534000</v>
       </c>
       <c r="I3" t="n">
-        <v>129176000</v>
+        <v>175433000</v>
       </c>
       <c r="J3" t="n">
-        <v>25659000</v>
+        <v>21432000</v>
       </c>
       <c r="K3" t="n">
-        <v>1743000</v>
+        <v>1293000</v>
       </c>
       <c r="L3" t="n">
-        <v>27402000</v>
+        <v>22725000</v>
       </c>
       <c r="M3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="N3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="O3" t="n">
-        <v>1182616000</v>
+        <v>1205891000</v>
       </c>
       <c r="P3" t="n">
-        <v>83897000</v>
+        <v>64458000</v>
       </c>
       <c r="Q3" t="n">
-        <v>101774000</v>
+        <v>152708000</v>
       </c>
       <c r="R3" t="n">
-        <v>978385013</v>
+        <v>981690335</v>
       </c>
       <c r="S3" t="n">
-        <v>978385013</v>
+        <v>981690335</v>
       </c>
       <c r="T3" t="n">
-        <v>0.1187</v>
+        <v>0.1573</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1187</v>
+        <v>0.1573</v>
       </c>
       <c r="V3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="W3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>116164000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>0</v>
-      </c>
+        <v>154462000</v>
+      </c>
+      <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="AB3" t="n">
-        <v>116164000</v>
+        <v>154462000</v>
       </c>
       <c r="AC3" t="n">
-        <v>11269000</v>
+        <v>19678000</v>
       </c>
       <c r="AD3" t="n">
-        <v>127433000</v>
+        <v>174140000</v>
       </c>
       <c r="AE3" t="n">
-        <v>25659000</v>
+        <v>21432000</v>
       </c>
       <c r="AF3" t="n">
-        <v>1743000</v>
+        <v>1293000</v>
       </c>
       <c r="AG3" t="n">
-        <v>27402000</v>
+        <v>22725000</v>
       </c>
       <c r="AH3" t="n">
-        <v>148840000</v>
+        <v>209818000</v>
       </c>
       <c r="AI3" t="n">
-        <v>609675000</v>
+        <v>559972000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>609675000</v>
+        <v>559972000</v>
       </c>
       <c r="AK3" t="n">
-        <v>447488000</v>
+        <v>406197000</v>
       </c>
       <c r="AL3" t="n">
-        <v>162187000</v>
+        <v>153775000</v>
       </c>
       <c r="AM3" t="n">
-        <v>758515000</v>
+        <v>769790000</v>
       </c>
       <c r="AN3" t="n">
-        <v>572941000</v>
+        <v>645919000</v>
       </c>
       <c r="AO3" t="n">
-        <v>1331456000</v>
+        <v>1415709000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1331456000</v>
+        <v>1415709000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
       </c>
       <c r="C4" t="n">
-        <v>0.113001</v>
+        <v>0.088431</v>
       </c>
       <c r="D4" t="n">
-        <v>216534000</v>
+        <v>174665000</v>
       </c>
       <c r="E4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="F4" t="n">
-        <v>41101000</v>
+        <v>45489000</v>
       </c>
       <c r="G4" t="n">
-        <v>645919000</v>
+        <v>572941000</v>
       </c>
       <c r="H4" t="n">
-        <v>216534000</v>
+        <v>174665000</v>
       </c>
       <c r="I4" t="n">
-        <v>175433000</v>
+        <v>129176000</v>
       </c>
       <c r="J4" t="n">
-        <v>21432000</v>
+        <v>25659000</v>
       </c>
       <c r="K4" t="n">
-        <v>1293000</v>
+        <v>1743000</v>
       </c>
       <c r="L4" t="n">
-        <v>22725000</v>
+        <v>27402000</v>
       </c>
       <c r="M4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="N4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="O4" t="n">
-        <v>1205891000</v>
+        <v>1182616000</v>
       </c>
       <c r="P4" t="n">
-        <v>64458000</v>
+        <v>83897000</v>
       </c>
       <c r="Q4" t="n">
-        <v>152708000</v>
+        <v>101774000</v>
       </c>
       <c r="R4" t="n">
-        <v>981690335</v>
+        <v>978385013</v>
       </c>
       <c r="S4" t="n">
-        <v>981690335</v>
+        <v>978385013</v>
       </c>
       <c r="T4" t="n">
-        <v>0.1573</v>
+        <v>0.1187</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1573</v>
+        <v>0.1187</v>
       </c>
       <c r="V4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="W4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>154462000</v>
-      </c>
-      <c r="Z4" t="inlineStr"/>
+        <v>116164000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
       <c r="AA4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="AB4" t="n">
-        <v>154462000</v>
+        <v>116164000</v>
       </c>
       <c r="AC4" t="n">
-        <v>19678000</v>
+        <v>11269000</v>
       </c>
       <c r="AD4" t="n">
-        <v>174140000</v>
+        <v>127433000</v>
       </c>
       <c r="AE4" t="n">
-        <v>21432000</v>
+        <v>25659000</v>
       </c>
       <c r="AF4" t="n">
-        <v>1293000</v>
+        <v>1743000</v>
       </c>
       <c r="AG4" t="n">
-        <v>22725000</v>
+        <v>27402000</v>
       </c>
       <c r="AH4" t="n">
-        <v>209818000</v>
+        <v>148840000</v>
       </c>
       <c r="AI4" t="n">
-        <v>559972000</v>
+        <v>609675000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>559972000</v>
+        <v>609675000</v>
       </c>
       <c r="AK4" t="n">
-        <v>406197000</v>
+        <v>447488000</v>
       </c>
       <c r="AL4" t="n">
-        <v>153775000</v>
+        <v>162187000</v>
       </c>
       <c r="AM4" t="n">
-        <v>769790000</v>
+        <v>758515000</v>
       </c>
       <c r="AN4" t="n">
-        <v>645919000</v>
+        <v>572941000</v>
       </c>
       <c r="AO4" t="n">
-        <v>1415709000</v>
+        <v>1331456000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1415709000</v>
+        <v>1331456000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
         <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>0.187</v>
+        <v>0.110447</v>
       </c>
       <c r="D5" t="n">
-        <v>294706000</v>
+        <v>158836000</v>
       </c>
       <c r="E5" t="n">
-        <v>221043000</v>
+        <v>93097000</v>
       </c>
       <c r="F5" t="n">
-        <v>32654000</v>
+        <v>52654000</v>
       </c>
       <c r="G5" t="n">
-        <v>503857000</v>
+        <v>524132000</v>
       </c>
       <c r="H5" t="n">
-        <v>294706000</v>
+        <v>158836000</v>
       </c>
       <c r="I5" t="n">
-        <v>262052000</v>
+        <v>106182000</v>
       </c>
       <c r="J5" t="n">
-        <v>20203000</v>
+        <v>24165000</v>
       </c>
       <c r="K5" t="n">
-        <v>1001000</v>
+        <v>1516000</v>
       </c>
       <c r="L5" t="n">
-        <v>21204000</v>
+        <v>25681000</v>
       </c>
       <c r="M5" t="n">
-        <v>221043000</v>
+        <v>93097000</v>
       </c>
       <c r="N5" t="n">
-        <v>221043000</v>
+        <v>93097000</v>
       </c>
       <c r="O5" t="n">
-        <v>1104559000</v>
+        <v>1111250000</v>
       </c>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="n">
-        <v>240848000</v>
+        <v>80501000</v>
       </c>
       <c r="R5" t="n">
-        <v>982114035</v>
+        <v>973844035</v>
       </c>
       <c r="S5" t="n">
-        <v>982114035</v>
+        <v>973844035</v>
       </c>
       <c r="T5" t="n">
-        <v>0.2251</v>
+        <v>0.0956</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2251</v>
+        <v>0.0956</v>
       </c>
       <c r="V5" t="n">
-        <v>221043000</v>
+        <v>93097000</v>
       </c>
       <c r="W5" t="n">
-        <v>221043000</v>
+        <v>93097000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>221043000</v>
-      </c>
-      <c r="Z5" t="inlineStr"/>
+        <v>93097000</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>-9000</v>
+      </c>
       <c r="AA5" t="n">
-        <v>221043000</v>
+        <v>93106000</v>
       </c>
       <c r="AB5" t="n">
-        <v>221043000</v>
+        <v>93106000</v>
       </c>
       <c r="AC5" t="n">
-        <v>40008000</v>
+        <v>11560000</v>
       </c>
       <c r="AD5" t="n">
-        <v>261051000</v>
+        <v>104666000</v>
       </c>
       <c r="AE5" t="n">
-        <v>20203000</v>
+        <v>24165000</v>
       </c>
       <c r="AF5" t="n">
-        <v>1001000</v>
+        <v>1516000</v>
       </c>
       <c r="AG5" t="n">
-        <v>21204000</v>
+        <v>25681000</v>
       </c>
       <c r="AH5" t="n">
-        <v>267625000</v>
+        <v>107863000</v>
       </c>
       <c r="AI5" t="n">
-        <v>600702000</v>
+        <v>587118000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>600702000</v>
+        <v>587118000</v>
       </c>
       <c r="AK5" t="n">
-        <v>430022000</v>
+        <v>431341000</v>
       </c>
       <c r="AL5" t="n">
-        <v>170680000</v>
+        <v>155777000</v>
       </c>
       <c r="AM5" t="n">
-        <v>868327000</v>
+        <v>694981000</v>
       </c>
       <c r="AN5" t="n">
-        <v>503857000</v>
+        <v>524132000</v>
       </c>
       <c r="AO5" t="n">
-        <v>1372184000</v>
+        <v>1219113000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1372184000</v>
+        <v>1219113000</v>
       </c>
     </row>
   </sheetData>
@@ -1482,54 +1482,48 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="n">
-        <v>973844035</v>
+        <v>982114000</v>
       </c>
       <c r="D2" t="n">
-        <v>973844035</v>
+        <v>982114000</v>
       </c>
       <c r="E2" t="n">
-        <v>26456000</v>
+        <v>25156000</v>
       </c>
       <c r="F2" t="n">
-        <v>4293404000</v>
+        <v>4580889000</v>
       </c>
       <c r="G2" t="n">
-        <v>4347155000</v>
+        <v>4624740000</v>
       </c>
       <c r="H2" t="n">
-        <v>1813300000</v>
+        <v>1879232000</v>
       </c>
       <c r="I2" t="n">
-        <v>4293404000</v>
+        <v>4580889000</v>
       </c>
       <c r="J2" t="n">
-        <v>26456000</v>
+        <v>25156000</v>
       </c>
       <c r="K2" t="n">
-        <v>4347155000</v>
+        <v>4624740000</v>
       </c>
       <c r="L2" t="n">
-        <v>4347155000</v>
+        <v>4624740000</v>
       </c>
       <c r="M2" t="n">
-        <v>4349283000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2128000</v>
-      </c>
+        <v>4624740000</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="O2" t="n">
-        <v>4347155000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>126425000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3096776000</v>
-      </c>
+        <v>4624740000</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="n">
         <v>1101358000</v>
       </c>
@@ -1537,582 +1531,592 @@
         <v>1101358000</v>
       </c>
       <c r="T2" t="n">
-        <v>797194000</v>
+        <v>1165583000</v>
       </c>
       <c r="U2" t="n">
-        <v>410076000</v>
+        <v>490641000</v>
       </c>
       <c r="V2" t="n">
-        <v>46559000</v>
+        <v>31862000</v>
       </c>
       <c r="W2" t="n">
-        <v>354392000</v>
+        <v>447608000</v>
       </c>
       <c r="X2" t="n">
-        <v>9125000</v>
+        <v>11171000</v>
       </c>
       <c r="Y2" t="n">
-        <v>9125000</v>
+        <v>11171000</v>
       </c>
       <c r="Z2" t="n">
-        <v>387118000</v>
+        <v>674942000</v>
       </c>
       <c r="AA2" t="n">
-        <v>17331000</v>
+        <v>13985000</v>
       </c>
       <c r="AB2" t="n">
-        <v>17331000</v>
+        <v>13985000</v>
       </c>
       <c r="AC2" t="n">
-        <v>230252000</v>
+        <v>295511000</v>
       </c>
       <c r="AD2" t="n">
-        <v>173318000</v>
+        <v>238696000</v>
       </c>
       <c r="AE2" t="n">
-        <v>7377000</v>
+        <v>8221000</v>
       </c>
       <c r="AF2" t="n">
-        <v>49557000</v>
+        <v>48594000</v>
       </c>
       <c r="AG2" t="n">
-        <v>5146477000</v>
+        <v>5790323000</v>
       </c>
       <c r="AH2" t="n">
-        <v>2946059000</v>
+        <v>3236149000</v>
       </c>
       <c r="AI2" t="n">
-        <v>55889000</v>
-      </c>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
+        <v>46814000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>6947000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>6947000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>2604529000</v>
+        <v>2994394000</v>
       </c>
       <c r="AM2" t="n">
-        <v>53751000</v>
+        <v>43851000</v>
       </c>
       <c r="AN2" t="n">
-        <v>53751000</v>
+        <v>43851000</v>
       </c>
       <c r="AO2" t="n">
-        <v>231890000</v>
+        <v>144143000</v>
       </c>
       <c r="AP2" t="n">
-        <v>-413891000</v>
+        <v>-397453000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>645781000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>45577000</v>
-      </c>
+        <v>541596000</v>
+      </c>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>261584000</v>
+        <v>250112000</v>
       </c>
       <c r="AU2" t="n">
-        <v>20178000</v>
+        <v>22233000</v>
       </c>
       <c r="AV2" t="n">
-        <v>318442000</v>
+        <v>269251000</v>
       </c>
       <c r="AW2" t="n">
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>2200418000</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>2554174000</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>715807000</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>1310000</v>
+        <v>20687000</v>
       </c>
       <c r="BA2" t="n">
-        <v>28894000</v>
+        <v>79795000</v>
       </c>
       <c r="BB2" t="n">
-        <v>973148000</v>
+        <v>195886000</v>
       </c>
       <c r="BC2" t="n">
-        <v>963476000</v>
+        <v>174299000</v>
       </c>
       <c r="BD2" t="n">
-        <v>8397000</v>
+        <v>18821000</v>
       </c>
       <c r="BE2" t="n">
-        <v>1275000</v>
+        <v>2766000</v>
       </c>
       <c r="BF2" t="n">
-        <v>41239000</v>
+        <v>69772000</v>
       </c>
       <c r="BG2" t="n">
-        <v>16622000</v>
+        <v>41135000</v>
       </c>
       <c r="BH2" t="n">
-        <v>88669000</v>
+        <v>100565000</v>
       </c>
       <c r="BI2" t="n">
-        <v>-623000</v>
+        <v>-1420000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>89292000</v>
+        <v>101985000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1050536000</v>
+        <v>1330527000</v>
       </c>
       <c r="BL2" t="n">
-        <v>734144000</v>
+        <v>876185000</v>
       </c>
       <c r="BM2" t="n">
-        <v>316392000</v>
+        <v>454342000</v>
       </c>
       <c r="BN2" t="n">
-        <v>194942000</v>
+        <v>16155000</v>
       </c>
       <c r="BO2" t="n">
-        <v>121450000</v>
+        <v>438187000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
-      </c>
-      <c r="B3" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="n">
+        <v>978436035</v>
+      </c>
+      <c r="D3" t="n">
+        <v>978436035</v>
+      </c>
+      <c r="E3" t="n">
+        <v>49677000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4398107000</v>
+      </c>
+      <c r="G3" t="n">
+        <v>4447383000</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1833141000</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4398107000</v>
+      </c>
+      <c r="J3" t="n">
+        <v>49677000</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4447383000</v>
+      </c>
+      <c r="L3" t="n">
+        <v>4447383000</v>
+      </c>
+      <c r="M3" t="n">
+        <v>4447383000</v>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
+        <v>4447383000</v>
+      </c>
+      <c r="P3" t="n">
+        <v>117867000</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>3038730000</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1096939000</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1096939000</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1043404000</v>
+      </c>
+      <c r="U3" t="n">
+        <v>456576000</v>
+      </c>
+      <c r="V3" t="n">
+        <v>26152000</v>
+      </c>
+      <c r="W3" t="n">
+        <v>399376000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>31048000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>31048000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>586828000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>18629000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>18629000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>299081000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>227776000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>24054000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>47251000</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>5490787000</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>3070818000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>57478000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>5432000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>5432000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>2775582000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>49276000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49276000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>183050000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-387072000</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>570122000</v>
+      </c>
+      <c r="AR3" t="n">
         <v>0</v>
       </c>
-      <c r="C3" t="n">
-        <v>973844035</v>
-      </c>
-      <c r="D3" t="n">
-        <v>973844035</v>
-      </c>
-      <c r="E3" t="n">
-        <v>44261000</v>
-      </c>
-      <c r="F3" t="n">
-        <v>4347280000</v>
-      </c>
-      <c r="G3" t="n">
-        <v>4404764000</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1818053000</v>
-      </c>
-      <c r="I3" t="n">
-        <v>4347280000</v>
-      </c>
-      <c r="J3" t="n">
-        <v>44261000</v>
-      </c>
-      <c r="K3" t="n">
-        <v>4404764000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>4404764000</v>
-      </c>
-      <c r="M3" t="n">
-        <v>4404764000</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>4404764000</v>
-      </c>
-      <c r="P3" t="n">
-        <v>118658000</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>3062265000</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1101358000</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1101358000</v>
-      </c>
-      <c r="T3" t="n">
-        <v>876992000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>429149000</v>
-      </c>
-      <c r="V3" t="n">
-        <v>30995000</v>
-      </c>
-      <c r="W3" t="n">
-        <v>375325000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>22829000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>22829000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>447843000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>21432000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>21432000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>215282000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>172470000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>8207000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>34605000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>5281756000</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>3015860000</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>55873000</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="n">
-        <v>2686658000</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>57484000</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>57484000</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>215845000</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>-397318000</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>613163000</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>18472000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+      <c r="AS3" t="n">
+        <v>232326000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>252669000</v>
+        <v>241966000</v>
       </c>
       <c r="AU3" t="n">
-        <v>34111000</v>
+        <v>37074000</v>
       </c>
       <c r="AV3" t="n">
-        <v>307911000</v>
+        <v>291082000</v>
       </c>
       <c r="AW3" t="n">
         <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>2265896000</v>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+        <v>2419969000</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>767938000</v>
+      </c>
       <c r="AZ3" t="n">
-        <v>10208000</v>
+        <v>26186000</v>
       </c>
       <c r="BA3" t="n">
-        <v>40812000</v>
+        <v>68502000</v>
       </c>
       <c r="BB3" t="n">
-        <v>956329000</v>
+        <v>972516000</v>
       </c>
       <c r="BC3" t="n">
-        <v>939795000</v>
+        <v>957983000</v>
       </c>
       <c r="BD3" t="n">
-        <v>14688000</v>
+        <v>12876000</v>
       </c>
       <c r="BE3" t="n">
-        <v>1846000</v>
+        <v>1657000</v>
       </c>
       <c r="BF3" t="n">
-        <v>65073000</v>
+        <v>73046000</v>
       </c>
       <c r="BG3" t="n">
-        <v>15152000</v>
+        <v>3938000</v>
       </c>
       <c r="BH3" t="n">
-        <v>99729000</v>
+        <v>125091000</v>
       </c>
       <c r="BI3" t="n">
-        <v>-1079000</v>
+        <v>-2195000</v>
       </c>
       <c r="BJ3" t="n">
-        <v>100808000</v>
+        <v>127286000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1078593000</v>
+        <v>1150690000</v>
       </c>
       <c r="BL3" t="n">
-        <v>721494000</v>
+        <v>840885000</v>
       </c>
       <c r="BM3" t="n">
-        <v>357099000</v>
+        <v>309805000</v>
       </c>
       <c r="BN3" t="n">
-        <v>59575000</v>
+        <v>51726000</v>
       </c>
       <c r="BO3" t="n">
-        <v>297524000</v>
+        <v>258079000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
-      </c>
-      <c r="B4" t="inlineStr"/>
+        <v>45291</v>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
       <c r="C4" t="n">
-        <v>978436035</v>
+        <v>973844035</v>
       </c>
       <c r="D4" t="n">
-        <v>978436035</v>
+        <v>973844035</v>
       </c>
       <c r="E4" t="n">
-        <v>49677000</v>
+        <v>44261000</v>
       </c>
       <c r="F4" t="n">
-        <v>4398107000</v>
+        <v>4347280000</v>
       </c>
       <c r="G4" t="n">
-        <v>4447383000</v>
+        <v>4404764000</v>
       </c>
       <c r="H4" t="n">
-        <v>1833141000</v>
+        <v>1818053000</v>
       </c>
       <c r="I4" t="n">
-        <v>4398107000</v>
+        <v>4347280000</v>
       </c>
       <c r="J4" t="n">
-        <v>49677000</v>
+        <v>44261000</v>
       </c>
       <c r="K4" t="n">
-        <v>4447383000</v>
+        <v>4404764000</v>
       </c>
       <c r="L4" t="n">
-        <v>4447383000</v>
+        <v>4404764000</v>
       </c>
       <c r="M4" t="n">
-        <v>4447383000</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+        <v>4404764000</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
       <c r="O4" t="n">
-        <v>4447383000</v>
+        <v>4404764000</v>
       </c>
       <c r="P4" t="n">
-        <v>117867000</v>
+        <v>118658000</v>
       </c>
       <c r="Q4" t="n">
-        <v>3038730000</v>
+        <v>3062265000</v>
       </c>
       <c r="R4" t="n">
-        <v>1096939000</v>
+        <v>1101358000</v>
       </c>
       <c r="S4" t="n">
-        <v>1096939000</v>
+        <v>1101358000</v>
       </c>
       <c r="T4" t="n">
-        <v>1043404000</v>
+        <v>876992000</v>
       </c>
       <c r="U4" t="n">
-        <v>456576000</v>
+        <v>429149000</v>
       </c>
       <c r="V4" t="n">
-        <v>26152000</v>
+        <v>30995000</v>
       </c>
       <c r="W4" t="n">
-        <v>399376000</v>
+        <v>375325000</v>
       </c>
       <c r="X4" t="n">
-        <v>31048000</v>
+        <v>22829000</v>
       </c>
       <c r="Y4" t="n">
-        <v>31048000</v>
+        <v>22829000</v>
       </c>
       <c r="Z4" t="n">
-        <v>586828000</v>
+        <v>447843000</v>
       </c>
       <c r="AA4" t="n">
-        <v>18629000</v>
+        <v>21432000</v>
       </c>
       <c r="AB4" t="n">
-        <v>18629000</v>
+        <v>21432000</v>
       </c>
       <c r="AC4" t="n">
-        <v>299081000</v>
+        <v>215282000</v>
       </c>
       <c r="AD4" t="n">
-        <v>227776000</v>
+        <v>172470000</v>
       </c>
       <c r="AE4" t="n">
-        <v>24054000</v>
+        <v>8207000</v>
       </c>
       <c r="AF4" t="n">
-        <v>47251000</v>
+        <v>34605000</v>
       </c>
       <c r="AG4" t="n">
-        <v>5490787000</v>
+        <v>5281756000</v>
       </c>
       <c r="AH4" t="n">
-        <v>3070818000</v>
+        <v>3015860000</v>
       </c>
       <c r="AI4" t="n">
-        <v>57478000</v>
+        <v>55873000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5432000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>5432000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>2775582000</v>
+        <v>2686658000</v>
       </c>
       <c r="AM4" t="n">
-        <v>49276000</v>
+        <v>57484000</v>
       </c>
       <c r="AN4" t="n">
-        <v>49276000</v>
+        <v>57484000</v>
       </c>
       <c r="AO4" t="n">
-        <v>183050000</v>
+        <v>215845000</v>
       </c>
       <c r="AP4" t="n">
-        <v>-387072000</v>
+        <v>-397318000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>570122000</v>
+        <v>613163000</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>232326000</v>
-      </c>
+        <v>18472000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>241966000</v>
+        <v>252669000</v>
       </c>
       <c r="AU4" t="n">
-        <v>37074000</v>
+        <v>34111000</v>
       </c>
       <c r="AV4" t="n">
-        <v>291082000</v>
+        <v>307911000</v>
       </c>
       <c r="AW4" t="n">
         <v>0</v>
       </c>
       <c r="AX4" t="n">
-        <v>2419969000</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>767938000</v>
-      </c>
+        <v>2265896000</v>
+      </c>
+      <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>26186000</v>
+        <v>10208000</v>
       </c>
       <c r="BA4" t="n">
-        <v>68502000</v>
+        <v>40812000</v>
       </c>
       <c r="BB4" t="n">
-        <v>972516000</v>
+        <v>956329000</v>
       </c>
       <c r="BC4" t="n">
-        <v>957983000</v>
+        <v>939795000</v>
       </c>
       <c r="BD4" t="n">
-        <v>12876000</v>
+        <v>14688000</v>
       </c>
       <c r="BE4" t="n">
-        <v>1657000</v>
+        <v>1846000</v>
       </c>
       <c r="BF4" t="n">
-        <v>73046000</v>
+        <v>65073000</v>
       </c>
       <c r="BG4" t="n">
-        <v>3938000</v>
+        <v>15152000</v>
       </c>
       <c r="BH4" t="n">
-        <v>125091000</v>
+        <v>99729000</v>
       </c>
       <c r="BI4" t="n">
-        <v>-2195000</v>
+        <v>-1079000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>127286000</v>
+        <v>100808000</v>
       </c>
       <c r="BK4" t="n">
-        <v>1150690000</v>
+        <v>1078593000</v>
       </c>
       <c r="BL4" t="n">
-        <v>840885000</v>
+        <v>721494000</v>
       </c>
       <c r="BM4" t="n">
-        <v>309805000</v>
+        <v>357099000</v>
       </c>
       <c r="BN4" t="n">
-        <v>51726000</v>
+        <v>59575000</v>
       </c>
       <c r="BO4" t="n">
-        <v>258079000</v>
+        <v>297524000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>982114000</v>
+        <v>973844035</v>
       </c>
       <c r="D5" t="n">
-        <v>982114000</v>
+        <v>973844035</v>
       </c>
       <c r="E5" t="n">
-        <v>25156000</v>
+        <v>26456000</v>
       </c>
       <c r="F5" t="n">
-        <v>4580889000</v>
+        <v>4293404000</v>
       </c>
       <c r="G5" t="n">
-        <v>4624740000</v>
+        <v>4347155000</v>
       </c>
       <c r="H5" t="n">
-        <v>1879232000</v>
+        <v>1813300000</v>
       </c>
       <c r="I5" t="n">
-        <v>4580889000</v>
+        <v>4293404000</v>
       </c>
       <c r="J5" t="n">
-        <v>25156000</v>
+        <v>26456000</v>
       </c>
       <c r="K5" t="n">
-        <v>4624740000</v>
+        <v>4347155000</v>
       </c>
       <c r="L5" t="n">
-        <v>4624740000</v>
+        <v>4347155000</v>
       </c>
       <c r="M5" t="n">
-        <v>4624740000</v>
-      </c>
-      <c r="N5" t="inlineStr"/>
+        <v>4349283000</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2128000</v>
+      </c>
       <c r="O5" t="n">
-        <v>4624740000</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
+        <v>4347155000</v>
+      </c>
+      <c r="P5" t="n">
+        <v>126425000</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>3096776000</v>
+      </c>
       <c r="R5" t="n">
         <v>1101358000</v>
       </c>
@@ -2120,144 +2124,140 @@
         <v>1101358000</v>
       </c>
       <c r="T5" t="n">
-        <v>1165583000</v>
+        <v>797194000</v>
       </c>
       <c r="U5" t="n">
-        <v>490641000</v>
+        <v>410076000</v>
       </c>
       <c r="V5" t="n">
-        <v>31862000</v>
+        <v>46559000</v>
       </c>
       <c r="W5" t="n">
-        <v>447608000</v>
+        <v>354392000</v>
       </c>
       <c r="X5" t="n">
-        <v>11171000</v>
+        <v>9125000</v>
       </c>
       <c r="Y5" t="n">
-        <v>11171000</v>
+        <v>9125000</v>
       </c>
       <c r="Z5" t="n">
-        <v>674942000</v>
+        <v>387118000</v>
       </c>
       <c r="AA5" t="n">
-        <v>13985000</v>
+        <v>17331000</v>
       </c>
       <c r="AB5" t="n">
-        <v>13985000</v>
+        <v>17331000</v>
       </c>
       <c r="AC5" t="n">
-        <v>295511000</v>
+        <v>230252000</v>
       </c>
       <c r="AD5" t="n">
-        <v>238696000</v>
+        <v>173318000</v>
       </c>
       <c r="AE5" t="n">
-        <v>8221000</v>
+        <v>7377000</v>
       </c>
       <c r="AF5" t="n">
-        <v>48594000</v>
+        <v>49557000</v>
       </c>
       <c r="AG5" t="n">
-        <v>5790323000</v>
+        <v>5146477000</v>
       </c>
       <c r="AH5" t="n">
-        <v>3236149000</v>
+        <v>2946059000</v>
       </c>
       <c r="AI5" t="n">
-        <v>46814000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>6947000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>6947000</v>
-      </c>
+        <v>55889000</v>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
       <c r="AL5" t="n">
-        <v>2994394000</v>
+        <v>2604529000</v>
       </c>
       <c r="AM5" t="n">
-        <v>43851000</v>
+        <v>53751000</v>
       </c>
       <c r="AN5" t="n">
-        <v>43851000</v>
+        <v>53751000</v>
       </c>
       <c r="AO5" t="n">
-        <v>144143000</v>
+        <v>231890000</v>
       </c>
       <c r="AP5" t="n">
-        <v>-397453000</v>
+        <v>-413891000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>541596000</v>
-      </c>
-      <c r="AR5" t="inlineStr"/>
+        <v>645781000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>45577000</v>
+      </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
-        <v>250112000</v>
+        <v>261584000</v>
       </c>
       <c r="AU5" t="n">
-        <v>22233000</v>
+        <v>20178000</v>
       </c>
       <c r="AV5" t="n">
-        <v>269251000</v>
+        <v>318442000</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
       </c>
       <c r="AX5" t="n">
-        <v>2554174000</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>715807000</v>
-      </c>
+        <v>2200418000</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>20687000</v>
+        <v>1310000</v>
       </c>
       <c r="BA5" t="n">
-        <v>79795000</v>
+        <v>28894000</v>
       </c>
       <c r="BB5" t="n">
-        <v>195886000</v>
+        <v>973148000</v>
       </c>
       <c r="BC5" t="n">
-        <v>174299000</v>
+        <v>963476000</v>
       </c>
       <c r="BD5" t="n">
-        <v>18821000</v>
+        <v>8397000</v>
       </c>
       <c r="BE5" t="n">
-        <v>2766000</v>
+        <v>1275000</v>
       </c>
       <c r="BF5" t="n">
-        <v>69772000</v>
+        <v>41239000</v>
       </c>
       <c r="BG5" t="n">
-        <v>41135000</v>
+        <v>16622000</v>
       </c>
       <c r="BH5" t="n">
-        <v>100565000</v>
+        <v>88669000</v>
       </c>
       <c r="BI5" t="n">
-        <v>-1420000</v>
+        <v>-623000</v>
       </c>
       <c r="BJ5" t="n">
-        <v>101985000</v>
+        <v>89292000</v>
       </c>
       <c r="BK5" t="n">
-        <v>1330527000</v>
+        <v>1050536000</v>
       </c>
       <c r="BL5" t="n">
-        <v>876185000</v>
+        <v>734144000</v>
       </c>
       <c r="BM5" t="n">
-        <v>454342000</v>
+        <v>316392000</v>
       </c>
       <c r="BN5" t="n">
-        <v>16155000</v>
+        <v>194942000</v>
       </c>
       <c r="BO5" t="n">
-        <v>438187000</v>
+        <v>121450000</v>
       </c>
     </row>
   </sheetData>
@@ -2463,40 +2463,38 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>55301000</v>
+        <v>189602000</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-51746000</v>
+        <v>-12716000</v>
       </c>
       <c r="E2" t="n">
-        <v>316392000</v>
+        <v>454342000</v>
       </c>
       <c r="F2" t="n">
-        <v>357099000</v>
+        <v>492715000</v>
       </c>
       <c r="G2" t="n">
-        <v>-12787000</v>
+        <v>19153000</v>
       </c>
       <c r="H2" t="n">
-        <v>-27920000</v>
+        <v>-57526000</v>
       </c>
       <c r="I2" t="n">
-        <v>-77607000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>2119000</v>
-      </c>
+        <v>-116812000</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>-58431000</v>
+        <v>-103123000</v>
       </c>
       <c r="L2" t="n">
-        <v>-58431000</v>
+        <v>-103123000</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -2505,338 +2503,336 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>-57360000</v>
+        <v>-143032000</v>
       </c>
       <c r="P2" t="n">
-        <v>8898000</v>
+        <v>-20687000</v>
       </c>
       <c r="Q2" t="n">
-        <v>27702000</v>
+        <v>18655000</v>
       </c>
       <c r="R2" t="n">
-        <v>-27572000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>944103000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-971675000</v>
-      </c>
+        <v>-117089000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
       <c r="U2" t="n">
-        <v>-5943000</v>
+        <v>-11365000</v>
       </c>
       <c r="V2" t="n">
-        <v>-5943000</v>
+        <v>-11365000</v>
       </c>
       <c r="W2" t="n">
-        <v>-51547000</v>
+        <v>-12546000</v>
       </c>
       <c r="X2" t="n">
-        <v>199000</v>
+        <v>170000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-51746000</v>
+        <v>-12716000</v>
       </c>
       <c r="Z2" t="n">
-        <v>107047000</v>
+        <v>202318000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-17994000</v>
+        <v>-52757000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-1516000</v>
+        <v>-1001000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-83026000</v>
+        <v>-4627000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-40230000</v>
+        <v>283589000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-84277000</v>
+        <v>-275075000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-24165000</v>
+        <v>-20203000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-113000</v>
+        <v>153000</v>
       </c>
       <c r="AH2" t="n">
-        <v>52654000</v>
+        <v>32654000</v>
       </c>
       <c r="AI2" t="n">
-        <v>52654000</v>
+        <v>32654000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27362000</v>
+        <v>26777000</v>
       </c>
       <c r="AK2" t="n">
-        <v>-2987000</v>
+        <v>304000</v>
       </c>
       <c r="AL2" t="n">
-        <v>104666000</v>
+        <v>261051000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>21325000</v>
+        <v>19105000</v>
       </c>
       <c r="C3" t="n">
-        <v>-4839000</v>
+        <v>-4384000</v>
       </c>
       <c r="D3" t="n">
-        <v>-44619000</v>
+        <v>-11859000</v>
       </c>
       <c r="E3" t="n">
-        <v>357099000</v>
+        <v>309805000</v>
       </c>
       <c r="F3" t="n">
-        <v>309805000</v>
+        <v>454342000</v>
       </c>
       <c r="G3" t="n">
-        <v>-10741000</v>
+        <v>-37949000</v>
       </c>
       <c r="H3" t="n">
-        <v>58035000</v>
+        <v>-106588000</v>
       </c>
       <c r="I3" t="n">
-        <v>-107620000</v>
+        <v>-124417000</v>
       </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>-83167000</v>
+        <v>-103122000</v>
       </c>
       <c r="L3" t="n">
-        <v>-83167000</v>
+        <v>-103122000</v>
       </c>
       <c r="M3" t="n">
-        <v>-4839000</v>
+        <v>-4384000</v>
       </c>
       <c r="N3" t="n">
-        <v>-4839000</v>
+        <v>-4384000</v>
       </c>
       <c r="O3" t="n">
-        <v>99711000</v>
+        <v>-13135000</v>
       </c>
       <c r="P3" t="n">
-        <v>15978000</v>
+        <v>-5499000</v>
       </c>
       <c r="Q3" t="n">
-        <v>22901000</v>
+        <v>25284000</v>
       </c>
       <c r="R3" t="n">
-        <v>111664000</v>
+        <v>-13543000</v>
       </c>
       <c r="S3" t="n">
-        <v>111664000</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-13543000</v>
+      </c>
       <c r="U3" t="n">
-        <v>-7612000</v>
+        <v>-7617000</v>
       </c>
       <c r="V3" t="n">
-        <v>-7612000</v>
+        <v>-7617000</v>
       </c>
       <c r="W3" t="n">
-        <v>-43220000</v>
+        <v>-11760000</v>
       </c>
       <c r="X3" t="n">
-        <v>1399000</v>
+        <v>99000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-44619000</v>
+        <v>-11859000</v>
       </c>
       <c r="Z3" t="n">
-        <v>65944000</v>
+        <v>30964000</v>
       </c>
       <c r="AA3" t="n">
-        <v>-48404000</v>
+        <v>-30703000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-1743000</v>
+        <v>-1293000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-102892000</v>
+        <v>-233503000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-121293000</v>
+        <v>-114858000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-44591000</v>
+        <v>-130642000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-25659000</v>
+        <v>-21432000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1122000</v>
+        <v>1028000</v>
       </c>
       <c r="AH3" t="n">
-        <v>45489000</v>
+        <v>41101000</v>
       </c>
       <c r="AI3" t="n">
-        <v>45489000</v>
+        <v>41101000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>47066000</v>
+        <v>57110000</v>
       </c>
       <c r="AK3" t="n">
-        <v>-852000</v>
+        <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>127433000</v>
+        <v>174140000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>19105000</v>
+        <v>21325000</v>
       </c>
       <c r="C4" t="n">
-        <v>-4384000</v>
+        <v>-4839000</v>
       </c>
       <c r="D4" t="n">
-        <v>-11859000</v>
+        <v>-44619000</v>
       </c>
       <c r="E4" t="n">
+        <v>357099000</v>
+      </c>
+      <c r="F4" t="n">
         <v>309805000</v>
       </c>
-      <c r="F4" t="n">
-        <v>454342000</v>
-      </c>
       <c r="G4" t="n">
-        <v>-37949000</v>
+        <v>-10741000</v>
       </c>
       <c r="H4" t="n">
-        <v>-106588000</v>
+        <v>58035000</v>
       </c>
       <c r="I4" t="n">
-        <v>-124417000</v>
+        <v>-107620000</v>
       </c>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>-103122000</v>
+        <v>-83167000</v>
       </c>
       <c r="L4" t="n">
-        <v>-103122000</v>
+        <v>-83167000</v>
       </c>
       <c r="M4" t="n">
-        <v>-4384000</v>
+        <v>-4839000</v>
       </c>
       <c r="N4" t="n">
-        <v>-4384000</v>
+        <v>-4839000</v>
       </c>
       <c r="O4" t="n">
-        <v>-13135000</v>
+        <v>99711000</v>
       </c>
       <c r="P4" t="n">
-        <v>-5499000</v>
+        <v>15978000</v>
       </c>
       <c r="Q4" t="n">
-        <v>25284000</v>
+        <v>22901000</v>
       </c>
       <c r="R4" t="n">
-        <v>-13543000</v>
+        <v>111664000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-13543000</v>
-      </c>
+        <v>111664000</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
       <c r="U4" t="n">
-        <v>-7617000</v>
+        <v>-7612000</v>
       </c>
       <c r="V4" t="n">
-        <v>-7617000</v>
+        <v>-7612000</v>
       </c>
       <c r="W4" t="n">
-        <v>-11760000</v>
+        <v>-43220000</v>
       </c>
       <c r="X4" t="n">
-        <v>99000</v>
+        <v>1399000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-11859000</v>
+        <v>-44619000</v>
       </c>
       <c r="Z4" t="n">
-        <v>30964000</v>
+        <v>65944000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-30703000</v>
+        <v>-48404000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-1293000</v>
+        <v>-1743000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-233503000</v>
+        <v>-102892000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-114858000</v>
+        <v>-121293000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-130642000</v>
+        <v>-44591000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-21432000</v>
+        <v>-25659000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1028000</v>
+        <v>-1122000</v>
       </c>
       <c r="AH4" t="n">
-        <v>41101000</v>
+        <v>45489000</v>
       </c>
       <c r="AI4" t="n">
-        <v>41101000</v>
+        <v>45489000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>57110000</v>
+        <v>47066000</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-852000</v>
       </c>
       <c r="AL4" t="n">
-        <v>174140000</v>
+        <v>127433000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>189602000</v>
+        <v>55301000</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-12716000</v>
+        <v>-51746000</v>
       </c>
       <c r="E5" t="n">
-        <v>454342000</v>
+        <v>316392000</v>
       </c>
       <c r="F5" t="n">
-        <v>492715000</v>
+        <v>357099000</v>
       </c>
       <c r="G5" t="n">
-        <v>19153000</v>
+        <v>-12787000</v>
       </c>
       <c r="H5" t="n">
-        <v>-57526000</v>
+        <v>-27920000</v>
       </c>
       <c r="I5" t="n">
-        <v>-116812000</v>
-      </c>
-      <c r="J5" t="inlineStr"/>
+        <v>-77607000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2119000</v>
+      </c>
       <c r="K5" t="n">
-        <v>-103123000</v>
+        <v>-58431000</v>
       </c>
       <c r="L5" t="n">
-        <v>-103123000</v>
+        <v>-58431000</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
@@ -2845,72 +2841,76 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-143032000</v>
+        <v>-57360000</v>
       </c>
       <c r="P5" t="n">
-        <v>-20687000</v>
+        <v>8898000</v>
       </c>
       <c r="Q5" t="n">
-        <v>18655000</v>
+        <v>27702000</v>
       </c>
       <c r="R5" t="n">
-        <v>-117089000</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+        <v>-27572000</v>
+      </c>
+      <c r="S5" t="n">
+        <v>944103000</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-971675000</v>
+      </c>
       <c r="U5" t="n">
-        <v>-11365000</v>
+        <v>-5943000</v>
       </c>
       <c r="V5" t="n">
-        <v>-11365000</v>
+        <v>-5943000</v>
       </c>
       <c r="W5" t="n">
-        <v>-12546000</v>
+        <v>-51547000</v>
       </c>
       <c r="X5" t="n">
-        <v>170000</v>
+        <v>199000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-12716000</v>
+        <v>-51746000</v>
       </c>
       <c r="Z5" t="n">
-        <v>202318000</v>
+        <v>107047000</v>
       </c>
       <c r="AA5" t="n">
-        <v>-52757000</v>
+        <v>-17994000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1001000</v>
+        <v>-1516000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4627000</v>
+        <v>-83026000</v>
       </c>
       <c r="AD5" t="n">
-        <v>283589000</v>
+        <v>-40230000</v>
       </c>
       <c r="AE5" t="n">
-        <v>-275075000</v>
+        <v>-84277000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-20203000</v>
+        <v>-24165000</v>
       </c>
       <c r="AG5" t="n">
-        <v>153000</v>
+        <v>-113000</v>
       </c>
       <c r="AH5" t="n">
-        <v>32654000</v>
+        <v>52654000</v>
       </c>
       <c r="AI5" t="n">
-        <v>32654000</v>
+        <v>52654000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>26777000</v>
+        <v>27362000</v>
       </c>
       <c r="AK5" t="n">
-        <v>304000</v>
+        <v>-2987000</v>
       </c>
       <c r="AL5" t="n">
-        <v>261051000</v>
+        <v>104666000</v>
       </c>
     </row>
   </sheetData>
@@ -3465,192 +3465,192 @@
       </c>
       <c r="DD1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
           <t>corporateActions</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>regularMarketTime</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>exchange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>messageBoardId</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>exchangeTimezoneName</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>exchangeTimezoneShortName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>gmtOffSetMilliseconds</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>market</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>esgPopulated</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>fullExchangeName</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>epsForward</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>fullExchangeName</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>longName</t>
         </is>
       </c>
       <c r="EP1" t="inlineStr">
@@ -3753,34 +3753,34 @@
         <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="V2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="W2" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Y2" t="n">
         <v>0.95</v>
       </c>
-      <c r="X2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.96</v>
-      </c>
       <c r="Z2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="AC2" t="n">
         <v>0.03</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="AE2" t="n">
         <v>1780531200</v>
@@ -3789,34 +3789,34 @@
         <v>0.6309</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.97</v>
+        <v>6.01</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.198</v>
+        <v>0.186</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.4642859</v>
+        <v>3.3214285</v>
       </c>
       <c r="AJ2" t="n">
-        <v>173000</v>
+        <v>280000</v>
       </c>
       <c r="AK2" t="n">
-        <v>173000</v>
+        <v>280000</v>
       </c>
       <c r="AL2" t="n">
-        <v>433258</v>
+        <v>435347</v>
       </c>
       <c r="AM2" t="n">
-        <v>306200</v>
+        <v>139300</v>
       </c>
       <c r="AN2" t="n">
-        <v>306200</v>
+        <v>139300</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.97</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -3825,13 +3825,13 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>944628672</v>
+        <v>905674880</v>
       </c>
       <c r="AT2" t="n">
-        <v>934890240</v>
+        <v>925151800</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="AV2" t="n">
         <v>1.15</v>
@@ -3843,19 +3843,19 @@
         <v>0.3</v>
       </c>
       <c r="AY2" t="n">
-        <v>0.87914383</v>
+        <v>0.84289044</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.0194</v>
+        <v>1.0218</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.97475</v>
+        <v>0.9736</v>
       </c>
       <c r="BB2" t="n">
         <v>0.025</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.026041668</v>
+        <v>0.02631579</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -3866,7 +3866,7 @@
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-183950320</v>
+        <v>-222904080</v>
       </c>
       <c r="BG2" t="n">
         <v>-0.0365</v>
@@ -3890,7 +3890,7 @@
         <v>4.562</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.21262605</v>
+        <v>0.20385797</v>
       </c>
       <c r="BO2" t="n">
         <v>1767139200</v>
@@ -3911,16 +3911,16 @@
         <v>0.28</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.171</v>
+        <v>-0.207</v>
       </c>
       <c r="BV2" t="n">
-        <v>-2.64</v>
+        <v>-3.199</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.021276593</v>
+        <v>-0.010416687</v>
       </c>
       <c r="BX2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BY2" t="n">
         <v>0.015</v>
@@ -3934,7 +3934,7 @@
         </is>
       </c>
       <c r="CB2" t="n">
-        <v>0.97</v>
+        <v>0.93</v>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
@@ -4035,141 +4035,141 @@
       </c>
       <c r="DD2" t="inlineStr">
         <is>
-          <t>[{'header': 'Dividend', 'message': '0533.HK announced a cash dividend of HKD 0.015 with an ex-date of Jun. 4, 2026', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1780502400000, 'amount': '0.015'}}]</t>
-        </is>
-      </c>
-      <c r="DE2" t="n">
-        <v>1780384246</v>
+          <t>GOLDLION HOLD</t>
+        </is>
+      </c>
+      <c r="DE2" t="inlineStr">
+        <is>
+          <t>Goldlion Holdings Limited</t>
+        </is>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="DG2" t="n">
+        <v>1782114522</v>
+      </c>
+      <c r="DH2" t="inlineStr">
+        <is>
           <t>HKG</t>
         </is>
       </c>
-      <c r="DG2" t="inlineStr">
+      <c r="DI2" t="inlineStr">
         <is>
           <t>finmb_4481087</t>
         </is>
       </c>
-      <c r="DH2" t="inlineStr">
+      <c r="DJ2" t="inlineStr">
         <is>
           <t>Asia/Hong_Kong</t>
         </is>
       </c>
-      <c r="DI2" t="inlineStr">
+      <c r="DK2" t="inlineStr">
         <is>
           <t>HKT</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
+      <c r="DL2" t="n">
         <v>28800000</v>
       </c>
-      <c r="DK2" t="inlineStr">
+      <c r="DM2" t="inlineStr">
         <is>
           <t>hk_market</t>
         </is>
       </c>
-      <c r="DL2" t="b">
+      <c r="DN2" t="b">
         <v>0</v>
       </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>GOLDLION HOLD</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>433258</v>
-      </c>
       <c r="DO2" t="n">
-        <v>0.050000012</v>
+        <v>-2.105261</v>
       </c>
       <c r="DP2" t="n">
-        <v>0.05434784</v>
+        <v>0.93</v>
       </c>
       <c r="DQ2" t="inlineStr">
         <is>
-          <t>0.92 - 1.15</t>
+          <t>PREPRE</t>
         </is>
       </c>
       <c r="DR2" t="n">
-        <v>-0.17999995</v>
+        <v>15</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0.1565217</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>2.1276593</v>
-      </c>
-      <c r="DU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="DT2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>946949400000</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>-0.01999998</v>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
+          <t>0.91 - 0.93</t>
+        </is>
+      </c>
+      <c r="DY2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DZ2" t="n">
+        <v>435347</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.01999998</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.021978</v>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>0.91 - 1.15</t>
+        </is>
+      </c>
+      <c r="ED2" t="n">
+        <v>-0.21999997</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>-0.19130433</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>-1.0416687</v>
+      </c>
+      <c r="EG2" t="n">
         <v>1741945680</v>
       </c>
-      <c r="DV2" t="n">
+      <c r="EH2" t="n">
         <v>1741945680</v>
       </c>
-      <c r="DW2" t="b">
+      <c r="EI2" t="b">
         <v>0</v>
       </c>
-      <c r="DX2" t="n">
+      <c r="EJ2" t="n">
         <v>-0.04</v>
       </c>
-      <c r="DY2" t="n">
+      <c r="EK2" t="n">
         <v>0.28</v>
       </c>
-      <c r="DZ2" t="n">
-        <v>-0.049399972</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.04845985</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>-0.0047499537</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>-0.004872997</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EF2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EH2" t="n">
-        <v>1.0416719</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="EJ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>946949400000</v>
-      </c>
       <c r="EL2" t="n">
-        <v>0.01000005</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>0.95 - 0.97</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Goldlion Holdings Limited</t>
-        </is>
+        <v>-0.091800034</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.089841485</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>-0.043599963</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>-0.044782214</v>
       </c>
       <c r="EP2" t="inlineStr"/>
     </row>
